--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_18-07-2025.xlsx
@@ -528,17 +528,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -576,25 +576,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -639,17 +639,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -687,25 +687,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -750,17 +750,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -798,25 +798,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -896,7 +896,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>£27.48</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -909,25 +909,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -972,17 +972,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1020,25 +1020,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1131,25 +1131,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1242,25 +1242,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1353,25 +1353,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1464,25 +1464,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1575,25 +1575,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1686,25 +1686,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1797,25 +1797,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1908,25 +1908,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2019,25 +2019,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2130,25 +2130,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
